--- a/apps/web/public/importmallar/importmall-legoresurser.xlsx
+++ b/apps/web/public/importmallar/importmall-legoresurser.xlsx
@@ -22,7 +22,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Obligatorisk. Legoresursens nummer, exakt tre siffror (textformatera kolumnen i Excel). Finns numret redan uppdateras legoresursen; används det av en maskin- eller personalresurs blir raden ett fel.</t>
+          <t xml:space="preserve">Obligatorisk. Legoresursens nummer, tre siffror. 1–2 siffror fylls ut med nollor (7 blir 007). Finns numret redan uppdateras legoresursen; används det av en maskin- eller personalresurs blir raden ett fel.</t>
         </r>
       </text>
     </comment>
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -134,6 +134,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -145,9 +146,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1" style="4"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1" style="4"/>
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
@@ -218,88 +219,73 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kolumner du inte behöver kan tas bort eller lämnas tomma, och kolumnernas ordning spelar ingen roll.</t>
+          <t xml:space="preserve">Ta bort kolumner du inte använder. Kolumnernas ordning spelar ingen roll.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t xml:space="preserve">En tom cell lämnar normalt värdet orört på en befintlig post, utom i kolumner där tomt betyder något: Huvudleverantör och Staffel: från antal/Staffel: pris (Inköpspriser), Partiformningsregel (Artiklar) samt Kalkyl och Tidsenhet med Uppdatera befintliga operationer (Operationer). Vad tomt betyder står vid varje kolumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tal skrivs med decimalkomma eller punkt. Obligatoriska kolumner måste finnas med och vara ifyllda på varje rad.</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Kolumn</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Obligatorisk</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Förklaring</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Exempel</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nummer</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ja</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Legoresursens nummer, exakt tre siffror (textformatera kolumnen i Excel). Finns numret redan uppdateras legoresursen; används det av en maskin- eller personalresurs blir raden ett fel.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Namn</t>
+          <t xml:space="preserve">Nummer</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legoresursens namn, max 100 tecken. Krävs för nya legoresurser. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Legoresursens nummer, tre siffror. 1–2 siffror fylls ut med nollor (7 blir 007). Finns numret redan uppdateras legoresursen; används det av en maskin- eller personalresurs blir raden ett fel.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pulverlackering, extern</t>
+          <t xml:space="preserve">910</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leverantörsnummer</t>
+          <t xml:space="preserve">Namn</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -309,19 +295,19 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Numret på den leverantör som utför legoarbetet — måste finnas i leverantörsregistret, importera leverantörerna först. Tom cell lämnar fältet orört.</t>
+          <t xml:space="preserve">Legoresursens namn, max 100 tecken. Krävs för nya legoresurser. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2003</t>
+          <t xml:space="preserve">Pulverlackering, extern</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ledtid (dagar)</t>
+          <t xml:space="preserve">Leverantörsnummer</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -331,19 +317,19 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arbetsdagar hos leverantören från avsändning till retur, decimalkomma eller punkt, aldrig negativ — används av planeringen och leveranstidskontrollen. Tom cell lämnar fältet orört.</t>
+          <t xml:space="preserve">Numret på den leverantör som utför legoarbetet — måste finnas i leverantörsregistret, importera leverantörerna först. Tom cell lämnar fältet orört.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2003</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kötid (dagar)</t>
+          <t xml:space="preserve">Ledtid (dagar)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -353,32 +339,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dagar innan arbetet påbörjas hos leverantören, decimalkomma eller punkt, aldrig negativ. Sparas som förvalsvärde; tom cell lämnar fältet orört.</t>
+          <t xml:space="preserve">Arbetsdagar hos leverantören från avsändning till retur, decimalkomma eller punkt, aldrig negativ — används av planeringen och leveranstidskontrollen. Tom cell lämnar fältet orört.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kötid (dagar)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dagar innan arbetet påbörjas hos leverantören, decimalkomma eller punkt, aldrig negativ. Sparas som förvalsvärde; tom cell lämnar fältet orört.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ledtid beställning (dagar)</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nej</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Dagar från beställning till att leverantören kan ta emot godset, decimalkomma eller punkt, aldrig negativ. Sparas som förvalsvärde; tom cell lämnar fältet orört.</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
